--- a/13_events_hazards.xlsx
+++ b/13_events_hazards.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R54c32f2b685b4b9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R6eec1d31118f4823"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="R61e7d1efcaeb4be9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R5d083b28e1c04347"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="R3e50e8797dfc4ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="Rfdeaa526a3084ae5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="Rdc67681b25974954"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R3b5715ee4d434906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="Rda9f86567a65474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="Rff7be74dc9e2458d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="1" r:id="R81fefc1772aa4a55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Locations" sheetId="2" r:id="R7e92f84546aa4868"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Asset Links" sheetId="3" r:id="Ree6e7f5511aa49fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Company Links" sheetId="4" r:id="R538f77c7a22346cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event System Links" sheetId="5" r:id="Rf276195771d947d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impact Chains" sheetId="6" r:id="R4e243b1778384eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Status History" sheetId="7" r:id="R86b814b329ac48cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R2f5e4e35339c4056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R5901a4f7b3414520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="10" r:id="R22533ce8a4054d5a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1324,7 +1324,7 @@
         <x:v>Saudi Arabia / Yemen</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>Jazan refinery / Jazan</x:v>
+        <x:v>Jazan Refinery / Jazan (mapped)</x:v>
       </x:c>
       <x:c r="K20" t="str">
         <x:v>Houthi Forces Attack Saudi Aramco's Jazan Refinery</x:v>
@@ -2519,6 +2519,159 @@
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>https://splash247.com/hormuz-attacks-reach-wartime-high/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C44"/>
+      <x:c r="D44" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>Explosions / strike activity near coastal and military infrastructure</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Security / Maritime / Energy</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Iran / Saudi Arabia</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>Hormozgan coast / Qeshm / Sirik / Minab / Taif</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Multiple explosions reported across Iran's Hormozgan coast and near Taif, Saudi Arabia</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>Iranian state media reported blasts at Qeshm Island, Sirik and Minab in Hormozgan province, while explosions were also reported near King Fahd Air Base and Taif in Saudi Arabia. Authorities in Hormozgan said sounds over Qeshm appeared to originate from the sea.</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>Escalation across the Hormuz coastal operating area; possible exposure of coastal, military and maritime infrastructure.</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>Higher Gulf war-risk exposure, stronger oil-price pressure and increased uncertainty for Hormuz shipping and regional energy flows.</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>SRC260910_025</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>https://gulfnews.com/world/mena/iran-rocked-by-explosions-as-trump-says-us-iran-war-wont-end-until-after-midterm-elections-1.500669266</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>2026-06-05</x:v>
+      </x:c>
+      <x:c r="C45"/>
+      <x:c r="D45" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>Drone attack on merchant cargo vessels</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Completed / monitoring</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>Security / Maritime</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Russia / Azerbaijan</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Sea of Azov / Taganrog Bay / Mariupol-Berdyansk approaches</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Drone attacks hit cargo vessels Natra and Zirkon in the Sea of Azov</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>Drone attacks struck the Palau-flagged cargo vessels Natra and Zirkon in the Sea of Azov. Azerbaijani authorities later confirmed four Azerbaijani citizens killed and four injured among 25 Azerbaijani crew members across the two vessels.</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Fatal merchant-vessel attack; vessel damage; search, rescue and recovery operations required.</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Demonstrates direct risk to civilian shipping in the Sea of Azov/Black Sea conflict environment and raises crew-safety and war-risk exposure.</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>SRC260910_026</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>https://oc-media.org/two-azerbaijani-citizens-killed-in-drone-attack-on-cargo-ship-in-black-sea/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C46"/>
+      <x:c r="D46" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Drone strike on port / oil-export infrastructure</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Security / Maritime / Energy</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Russia / Ukraine</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>Novorossiysk, Black Sea</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Ukraine targets Novorossiysk oil-export hub</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>Ukrainian drones struck infrastructure in and near Novorossiysk. Reporting cited four civilian deaths, damage to civil infrastructure, and a fire at a fuel-oil terminal; Ukrainian forces also said they struck the naval base.</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Port and fuel-terminal damage; potential disruption to oil-export and naval operations.</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Novorossiysk is a key Black Sea export hub; disruption can affect Russian crude/product flows and nearby CPC loadings carrying the majority of Kazakhstan's crude exports.</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>SRC260910_027</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>https://oilprice.com/Latest-Energy-News/World-News/Ukraine-Targets-Russias-Key-Black-Sea-Oil-Port.html</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3212,7 +3365,7 @@
         <x:v>EVT260910_001</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Jazan refinery / Jazan</x:v>
+        <x:v>Jazan Refinery / Jazan</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>Saudi Arabia</x:v>
@@ -3224,10 +3377,10 @@
         <x:v>42.551</x:v>
       </x:c>
       <x:c r="G20" t="str">
-        <x:v>Approximate refinery-area coordinate</x:v>
+        <x:v>Mapped location / approximate refinery-area coordinate</x:v>
       </x:c>
       <x:c r="H20" t="str">
-        <x:v>Approximate Jazan refinery-area marker for regional security map.</x:v>
+        <x:v>Mapped for Regional Security. Marker represents the Jazan refinery-area location for the Houthi attack event.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3734,6 +3887,162 @@
       </x:c>
       <x:c r="H43" t="str">
         <x:v>Location retained for event context; not plotted unless coordinates are available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>LOC260910_025A</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Qeshm Island / Qeshm</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>26.9581</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>56.2719</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>Island / city-level</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Reporting named Qeshm; marker is geographic context rather than strike-point precision.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>LOC260910_025B</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Sirik</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>26.5219</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>57.109</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Town-level</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>Reporting named Sirik; marker is town-level context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>LOC260910_025C</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>Minab</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>27.1467</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>57.0801</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>City-level</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Reporting named Minab; marker is city-level context.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>LOC260910_025D</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Taif</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Saudi Arabia</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>21.2703</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>40.4158</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>City-level</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>Explosions were reported near King Fahd Air Base and Taif; marker uses Taif city rather than a precise military-site coordinate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>LOC260910_026A</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Taganrog Bay / Sea of Azov</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E48" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F48" t="n">
+        <x:v>38.6</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>Sea-area / approximate theatre marker</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>Context marker for Sea of Azov vessel attacks; not a claimed strike-point coordinate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>LOC260910_027A</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Novorossiysk</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="E49" t="n">
+        <x:v>44.723</x:v>
+      </x:c>
+      <x:c r="F49" t="n">
+        <x:v>37.768</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>City / port-level</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>Port-city marker for the reported Novorossiysk strike; not a precise impact coordinate.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4821,6 +5130,84 @@
         <x:v>Two dry-bulk berth concession</x:v>
       </x:c>
     </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>EAL260910_026A</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>VESSEL_NATRA</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Natra</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Cargo vessel</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Merchant vessel struck in Sea of Azov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>EAL260910_026B</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>VESSEL_ZIRKON</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Zirkon</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Cargo vessel</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Merchant vessel struck in Sea of Azov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>EAL260910_027A</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>PORT_NOVOROSSIYSK</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Port of Novorossiysk</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>Port / oil-export hub</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Port and fuel-oil infrastructure struck</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6072,6 +6459,66 @@
         <x:v>SECURITY_ADVISORY</x:v>
       </x:c>
       <x:c r="F16" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>ESL260910_025</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>CORRIDOR_HORMUZ</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Strait of Hormuz</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>REGIONAL_SECURITY_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>ESL260910_026</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>SYS_BLACK_SEA_AZOV</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Black Sea / Sea of Azov merchant-shipping theatre</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>DIRECT_SECURITY_IMPACT</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>ESL260910_027</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>SYS_BLACK_SEA_ENERGY</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Black Sea energy-export system</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>DIRECT_SYSTEM_IMPACT</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
         <x:v>High</x:v>
       </x:c>
     </x:row>
@@ -6530,6 +6977,93 @@
         <x:v>Advisory → operational posture</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>CHAIN260910_025</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>EVT260910_025</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Explosions / strike activity across Hormozgan coast and Taif</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Heightened threat to coastal and military infrastructure</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Greater uncertainty around Hormuz approaches and regional air/maritime operating conditions</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>War-risk, routing and energy-market pressure</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Sustained Gulf trade and energy-flow disruption risk</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>Direct → regional → commercial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>CHAIN260910_026</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>EVT260910_026</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Drone attack on merchant vessels</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Crew fatalities and vessel damage</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>Search/rescue and recovery operations; heightened merchant-shipping caution</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Higher war-risk and crew-safety exposure in Sea of Azov traffic</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Reduced operating tolerance for civilian shipping near active strike zones</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>Direct → operational → commercial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>CHAIN260910_027</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>EVT260910_027</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Drone strike on Novorossiysk port/energy infrastructure</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Fuel-terminal and port damage</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Possible loading interruptions / operating restrictions</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Pressure on Russian Black Sea export capacity and CPC-related logistics</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Potential crude-flow disruption and higher Black Sea energy-shipping risk</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>Direct → logistics → energy-market</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -7599,6 +8133,20 @@
         <x:v>https://splash247.com/hormuz-attacks-reach-wartime-high/</x:v>
       </x:c>
     </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>SRC260910_025</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Gulf News</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Hormozgan / Qeshm / Sirik / Minab / Taif explosions</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>https://gulfnews.com/world/mena/iran-rocked-by-explosions-as-trump-says-us-iran-war-wont-end-until-after-midterm-elections-1.500669266</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
